--- a/compounds.xlsx
+++ b/compounds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ef049bac3ee44fb5/デスクトップ/構造クイズ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="14" documentId="8_{D4CA0FFB-8ADF-409B-8EC3-E330B2D69C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B569B73B-C9DF-4687-B1ED-7F0D6D8367CA}"/>
+  <xr:revisionPtr revIDLastSave="17" documentId="8_{D4CA0FFB-8ADF-409B-8EC3-E330B2D69C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC396342-1A80-4B1B-8D16-18AC9186294F}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{60308777-13F3-4883-9DF9-D5C4FE3A0F3D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="324" uniqueCount="320">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="431">
   <si>
     <t>structure</t>
   </si>
@@ -999,6 +999,339 @@
   </si>
   <si>
     <t>Tetrahydropyran</t>
+  </si>
+  <si>
+    <t>CN(C)C(=[N+](C)C)Oc1nnnc2ncccc12.F[P-](F)(F)(F)(F)F</t>
+  </si>
+  <si>
+    <t>HATU</t>
+  </si>
+  <si>
+    <t>1-[Bis(dimethylamino)methylene]-1H-1,2,3-triazolo[4,5-b]pyridinium 3-oxide hexafluorophosphate</t>
+  </si>
+  <si>
+    <t>O=C(n1ccnc1)n2ccnc2</t>
+  </si>
+  <si>
+    <t>CDI</t>
+  </si>
+  <si>
+    <t>1,1'-Carbonyldiimidazole</t>
+  </si>
+  <si>
+    <t>O=P(Oc1ccccc1)(Oc2ccccc2)N=[N+]=[N-]</t>
+  </si>
+  <si>
+    <t>DPPA</t>
+  </si>
+  <si>
+    <t>Diphenylphosphoryl azide</t>
+  </si>
+  <si>
+    <t>OC(C(F)(F)F)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>HFIP</t>
+  </si>
+  <si>
+    <t>1,1,1,3,3,3-Hexafluoro-2-propanol</t>
+  </si>
+  <si>
+    <t>CO[CH]1CCCC1</t>
+  </si>
+  <si>
+    <t>CPME</t>
+  </si>
+  <si>
+    <t>Cyclopentyl methyl ether</t>
+  </si>
+  <si>
+    <t>c1ccc(P(c2ccccc2)[c-]3cccc3)cc1.c4ccc(P(c5ccccc5)[c-]6cccc6)cc4.[Fe+2]</t>
+  </si>
+  <si>
+    <t>dppf</t>
+  </si>
+  <si>
+    <t>1,1'-Bis(diphenylphosphino)ferrocene</t>
+  </si>
+  <si>
+    <t>CC(C)c1cc(C(C)C)cc(C(C)C)c1-c2ccccc2P(C3CCCCC3)C4CCCCC4</t>
+  </si>
+  <si>
+    <t>XPhos</t>
+  </si>
+  <si>
+    <t>2-Dicyclohexylphosphino-2',4',6'-triisopropylbiphenyl</t>
+  </si>
+  <si>
+    <t>c1ccc(nc1)-c2ccccn2.c3ccc(nc3)-c4ccccn4.c5ccc(nc5)-c6ccccn6.[Ru+2]</t>
+  </si>
+  <si>
+    <t>Ru(bpy)3</t>
+  </si>
+  <si>
+    <t>Tris(bipyridine)ruthenium(II)</t>
+  </si>
+  <si>
+    <t>N#Cc1c2ccccc2c(C#N)c3ccccc13</t>
+  </si>
+  <si>
+    <t>DCA</t>
+  </si>
+  <si>
+    <t>9,10-Dicyanoanthracene</t>
+  </si>
+  <si>
+    <t>N#Cc1c(N2c3ccccc3c4ccccc24)c(C#N)c(N5c6ccccc6c7ccccc57)c(N8c9ccccc9c10ccccc810)c1(N11c12ccccc12c13ccccc1113)</t>
+  </si>
+  <si>
+    <t>4-CzIPN</t>
+  </si>
+  <si>
+    <t>1,2,3,5-Tetrakis(carbazol-9-yl)-4,6-dicyanobenzene</t>
+  </si>
+  <si>
+    <t>*C(=O)OCC=C</t>
+  </si>
+  <si>
+    <t>Alloc</t>
+  </si>
+  <si>
+    <t>Allyloxycarbonyl</t>
+  </si>
+  <si>
+    <t>*COCCOC</t>
+  </si>
+  <si>
+    <t>MEM</t>
+  </si>
+  <si>
+    <t>2-Methoxyethoxymethyl</t>
+  </si>
+  <si>
+    <t>C[Si](C)(C)Cl</t>
+  </si>
+  <si>
+    <t>TMSCl</t>
+  </si>
+  <si>
+    <t>Trimethylsilyl chloride</t>
+  </si>
+  <si>
+    <t>O=S(=O)(O)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>TfOH</t>
+  </si>
+  <si>
+    <t>Trifluoromethanesulfonic acid</t>
+  </si>
+  <si>
+    <t>O=C(OOC(=O)c1ccccc1)c2ccccc2</t>
+  </si>
+  <si>
+    <t>BPO</t>
+  </si>
+  <si>
+    <t>Benzoyl peroxide</t>
+  </si>
+  <si>
+    <t>CN1CCCN(C)C1=O</t>
+  </si>
+  <si>
+    <t>DMPU</t>
+  </si>
+  <si>
+    <t>1,3-Dimethyl-3,4,5,6-tetrahydro-2(1H)-pyrimidinone</t>
+  </si>
+  <si>
+    <t>Cn1ccnc1</t>
+  </si>
+  <si>
+    <t>NMI</t>
+  </si>
+  <si>
+    <t>1-Methylimidazole</t>
+  </si>
+  <si>
+    <t>CN(C)[P+](Oc1nnnc2ccccc12)(N(C)C)N(C)C.F[P-](F)(F)(F)(F)F</t>
+  </si>
+  <si>
+    <t>BOP</t>
+  </si>
+  <si>
+    <t>(Benzotriazol-1-yloxy)tris(dimethylamino)phosphonium hexafluorophosphate</t>
+  </si>
+  <si>
+    <t>c1ccc2c(c1)nnn2O[P+](N3CCCC3)(N4CCCC4)N5CCCC5.F[P-](F)(F)(F)(F)F</t>
+  </si>
+  <si>
+    <t>PyBOP</t>
+  </si>
+  <si>
+    <t>(Benzotriazol-1-yloxy)tripyrrolidinophosphonium hexafluorophosphate</t>
+  </si>
+  <si>
+    <t>CCC[P]1(=O)O[P](=O)(CCC)O[P](=O)(CCC)O1</t>
+  </si>
+  <si>
+    <t>T3P</t>
+  </si>
+  <si>
+    <t>Propylphosphonic anhydride</t>
+  </si>
+  <si>
+    <t>c1ccc(cc1)COC2=NC(=NC(=N2)OCc3ccccc3)OCc4ccccc4</t>
+  </si>
+  <si>
+    <t>TriBOT</t>
+  </si>
+  <si>
+    <t>2,4,6-Tris(benzyloxy)-1,3,5-triazine</t>
+  </si>
+  <si>
+    <t>[Li+].[AlH4-]</t>
+  </si>
+  <si>
+    <t>LAH</t>
+  </si>
+  <si>
+    <t>Lithium aluminium hydride</t>
+  </si>
+  <si>
+    <t>[Na+].[BH4-]</t>
+  </si>
+  <si>
+    <t>NaBH4</t>
+  </si>
+  <si>
+    <t>Sodium borohydride</t>
+  </si>
+  <si>
+    <t>CC(=O)O[B-](H)(OC(C)=O)OC(C)=O.[Na+]</t>
+  </si>
+  <si>
+    <t>STAB</t>
+  </si>
+  <si>
+    <t>Sodium triacetoxyborohydride</t>
+  </si>
+  <si>
+    <t>CCC(C)[B-](H)(C(C)CC)C(C)CC.[Li+]</t>
+  </si>
+  <si>
+    <t>L-Selectride</t>
+  </si>
+  <si>
+    <t>Lithium tri-sec-butylborohydride</t>
+  </si>
+  <si>
+    <t>C[Si](C)(C)[N-][Si](C)(C)C.[K+]</t>
+  </si>
+  <si>
+    <t>KHMDS</t>
+  </si>
+  <si>
+    <t>Potassium hexamethyldisilazide</t>
+  </si>
+  <si>
+    <t>C[Si](C)(C)[N-][Si](C)(C)C.[Na+]</t>
+  </si>
+  <si>
+    <t>NaHMDS</t>
+  </si>
+  <si>
+    <t>Sodium hexamethyldisilazide</t>
+  </si>
+  <si>
+    <t>CC(C)(C)[O-].[K+]</t>
+  </si>
+  <si>
+    <t>t-BuOK</t>
+  </si>
+  <si>
+    <t>Potassium tert-butoxide</t>
+  </si>
+  <si>
+    <t>F[N+]12CC[N+](CCl)(CC1)CC2.[B-](F)(F)(F)F.[B-](F)(F)(F)F</t>
+  </si>
+  <si>
+    <t>Selectfluor</t>
+  </si>
+  <si>
+    <t>1-Chloromethyl-4-fluoro-1,4-diazoniabicyclo[2.2.2]octane bis(tetrafluoroborate)</t>
+  </si>
+  <si>
+    <t>O=S(=O)(c1ccccc1)N(F)S(=O)(=O)c2ccccc2</t>
+  </si>
+  <si>
+    <t>NFSI</t>
+  </si>
+  <si>
+    <t>N-Fluorobenzenesulfonimide</t>
+  </si>
+  <si>
+    <t>CC(C)N=C=NC(C)C</t>
+  </si>
+  <si>
+    <t>DIC</t>
+  </si>
+  <si>
+    <t>N,N'-Diisopropylcarbodiimide</t>
+  </si>
+  <si>
+    <t>C[Si](C)(C)OS(=O)(=O)C(F)(F)F</t>
+  </si>
+  <si>
+    <t>TMSOTf</t>
+  </si>
+  <si>
+    <t>Trimethylsilyl trifluoromethanesulfonate</t>
+  </si>
+  <si>
+    <t>Cc1ccc(S(=O)(=O)Cl)cc1</t>
+  </si>
+  <si>
+    <t>TsCl</t>
+  </si>
+  <si>
+    <t>p-Toluenesulfonyl chloride</t>
+  </si>
+  <si>
+    <t>CS(=O)(=O)Cl</t>
+  </si>
+  <si>
+    <t>MsCl</t>
+  </si>
+  <si>
+    <t>Methanesulfonyl chloride</t>
+  </si>
+  <si>
+    <t>C[B]1OC(c2ccccc2)(c3ccccc3)C4CCCN14</t>
+  </si>
+  <si>
+    <t>CBS</t>
+  </si>
+  <si>
+    <t>Corey-Bakshi-Shibata catalyst (Me-CBS)</t>
+  </si>
+  <si>
+    <t>Cc1cc(C)c(c(C)c1)N2C=[C]N(C2)c3c(C)cc(C)cc3C</t>
+  </si>
+  <si>
+    <t>IMes</t>
+  </si>
+  <si>
+    <t>1,3-Bis(2,4,6-trimethylphenyl)imidazol-2-ylidene</t>
+  </si>
+  <si>
+    <t>CC(C)c1cccc(C(C)C)c1N2C=[C]N(C2)c3c(C(C)C)cccc3C(C)C</t>
+  </si>
+  <si>
+    <t>IPr</t>
+  </si>
+  <si>
+    <t>1,3-Bis(2,6-diisopropylphenyl)imidazol-2-ylidene</t>
   </si>
 </sst>
 </file>
@@ -1405,7 +1738,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A2CED0-FCDE-4C58-8502-7B6BD1A44430}">
-  <dimension ref="A1:C108"/>
+  <dimension ref="A1:C145"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -2596,6 +2929,413 @@
         <v>319</v>
       </c>
     </row>
+    <row r="109" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A109" t="s">
+        <v>320</v>
+      </c>
+      <c r="B109" t="s">
+        <v>321</v>
+      </c>
+      <c r="C109" t="s">
+        <v>322</v>
+      </c>
+    </row>
+    <row r="110" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A110" t="s">
+        <v>323</v>
+      </c>
+      <c r="B110" t="s">
+        <v>324</v>
+      </c>
+      <c r="C110" t="s">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="111" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A111" t="s">
+        <v>326</v>
+      </c>
+      <c r="B111" t="s">
+        <v>327</v>
+      </c>
+      <c r="C111" t="s">
+        <v>328</v>
+      </c>
+    </row>
+    <row r="112" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A112" t="s">
+        <v>329</v>
+      </c>
+      <c r="B112" t="s">
+        <v>330</v>
+      </c>
+      <c r="C112" t="s">
+        <v>331</v>
+      </c>
+    </row>
+    <row r="113" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A113" t="s">
+        <v>332</v>
+      </c>
+      <c r="B113" t="s">
+        <v>333</v>
+      </c>
+      <c r="C113" t="s">
+        <v>334</v>
+      </c>
+    </row>
+    <row r="114" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A114" t="s">
+        <v>335</v>
+      </c>
+      <c r="B114" t="s">
+        <v>336</v>
+      </c>
+      <c r="C114" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="115" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A115" t="s">
+        <v>338</v>
+      </c>
+      <c r="B115" t="s">
+        <v>339</v>
+      </c>
+      <c r="C115" t="s">
+        <v>340</v>
+      </c>
+    </row>
+    <row r="116" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A116" t="s">
+        <v>341</v>
+      </c>
+      <c r="B116" t="s">
+        <v>342</v>
+      </c>
+      <c r="C116" t="s">
+        <v>343</v>
+      </c>
+    </row>
+    <row r="117" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A117" t="s">
+        <v>344</v>
+      </c>
+      <c r="B117" t="s">
+        <v>345</v>
+      </c>
+      <c r="C117" t="s">
+        <v>346</v>
+      </c>
+    </row>
+    <row r="118" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A118" t="s">
+        <v>347</v>
+      </c>
+      <c r="B118" t="s">
+        <v>348</v>
+      </c>
+      <c r="C118" t="s">
+        <v>349</v>
+      </c>
+    </row>
+    <row r="119" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A119" t="s">
+        <v>350</v>
+      </c>
+      <c r="B119" t="s">
+        <v>351</v>
+      </c>
+      <c r="C119" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="120" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A120" t="s">
+        <v>353</v>
+      </c>
+      <c r="B120" t="s">
+        <v>354</v>
+      </c>
+      <c r="C120" t="s">
+        <v>355</v>
+      </c>
+    </row>
+    <row r="121" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A121" t="s">
+        <v>356</v>
+      </c>
+      <c r="B121" t="s">
+        <v>357</v>
+      </c>
+      <c r="C121" t="s">
+        <v>358</v>
+      </c>
+    </row>
+    <row r="122" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A122" t="s">
+        <v>359</v>
+      </c>
+      <c r="B122" t="s">
+        <v>360</v>
+      </c>
+      <c r="C122" t="s">
+        <v>361</v>
+      </c>
+    </row>
+    <row r="123" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A123" t="s">
+        <v>362</v>
+      </c>
+      <c r="B123" t="s">
+        <v>363</v>
+      </c>
+      <c r="C123" t="s">
+        <v>364</v>
+      </c>
+    </row>
+    <row r="124" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A124" t="s">
+        <v>365</v>
+      </c>
+      <c r="B124" t="s">
+        <v>366</v>
+      </c>
+      <c r="C124" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="125" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A125" t="s">
+        <v>368</v>
+      </c>
+      <c r="B125" t="s">
+        <v>369</v>
+      </c>
+      <c r="C125" t="s">
+        <v>370</v>
+      </c>
+    </row>
+    <row r="126" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A126" t="s">
+        <v>371</v>
+      </c>
+      <c r="B126" t="s">
+        <v>372</v>
+      </c>
+      <c r="C126" t="s">
+        <v>373</v>
+      </c>
+    </row>
+    <row r="127" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A127" t="s">
+        <v>374</v>
+      </c>
+      <c r="B127" t="s">
+        <v>375</v>
+      </c>
+      <c r="C127" t="s">
+        <v>376</v>
+      </c>
+    </row>
+    <row r="128" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A128" t="s">
+        <v>377</v>
+      </c>
+      <c r="B128" t="s">
+        <v>378</v>
+      </c>
+      <c r="C128" t="s">
+        <v>379</v>
+      </c>
+    </row>
+    <row r="129" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A129" t="s">
+        <v>380</v>
+      </c>
+      <c r="B129" t="s">
+        <v>381</v>
+      </c>
+      <c r="C129" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="130" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A130" t="s">
+        <v>383</v>
+      </c>
+      <c r="B130" t="s">
+        <v>384</v>
+      </c>
+      <c r="C130" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="131" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A131" t="s">
+        <v>386</v>
+      </c>
+      <c r="B131" t="s">
+        <v>387</v>
+      </c>
+      <c r="C131" t="s">
+        <v>388</v>
+      </c>
+    </row>
+    <row r="132" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A132" t="s">
+        <v>389</v>
+      </c>
+      <c r="B132" t="s">
+        <v>390</v>
+      </c>
+      <c r="C132" t="s">
+        <v>391</v>
+      </c>
+    </row>
+    <row r="133" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A133" t="s">
+        <v>392</v>
+      </c>
+      <c r="B133" t="s">
+        <v>393</v>
+      </c>
+      <c r="C133" t="s">
+        <v>394</v>
+      </c>
+    </row>
+    <row r="134" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A134" t="s">
+        <v>395</v>
+      </c>
+      <c r="B134" t="s">
+        <v>396</v>
+      </c>
+      <c r="C134" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="135" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A135" t="s">
+        <v>398</v>
+      </c>
+      <c r="B135" t="s">
+        <v>399</v>
+      </c>
+      <c r="C135" t="s">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="136" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A136" t="s">
+        <v>401</v>
+      </c>
+      <c r="B136" t="s">
+        <v>402</v>
+      </c>
+      <c r="C136" t="s">
+        <v>403</v>
+      </c>
+    </row>
+    <row r="137" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A137" t="s">
+        <v>404</v>
+      </c>
+      <c r="B137" t="s">
+        <v>405</v>
+      </c>
+      <c r="C137" t="s">
+        <v>406</v>
+      </c>
+    </row>
+    <row r="138" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A138" t="s">
+        <v>407</v>
+      </c>
+      <c r="B138" t="s">
+        <v>408</v>
+      </c>
+      <c r="C138" t="s">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="139" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A139" t="s">
+        <v>410</v>
+      </c>
+      <c r="B139" t="s">
+        <v>411</v>
+      </c>
+      <c r="C139" t="s">
+        <v>412</v>
+      </c>
+    </row>
+    <row r="140" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A140" t="s">
+        <v>413</v>
+      </c>
+      <c r="B140" t="s">
+        <v>414</v>
+      </c>
+      <c r="C140" t="s">
+        <v>415</v>
+      </c>
+    </row>
+    <row r="141" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A141" t="s">
+        <v>416</v>
+      </c>
+      <c r="B141" t="s">
+        <v>417</v>
+      </c>
+      <c r="C141" t="s">
+        <v>418</v>
+      </c>
+    </row>
+    <row r="142" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A142" t="s">
+        <v>419</v>
+      </c>
+      <c r="B142" t="s">
+        <v>420</v>
+      </c>
+      <c r="C142" t="s">
+        <v>421</v>
+      </c>
+    </row>
+    <row r="143" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A143" t="s">
+        <v>422</v>
+      </c>
+      <c r="B143" t="s">
+        <v>423</v>
+      </c>
+      <c r="C143" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="144" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A144" t="s">
+        <v>425</v>
+      </c>
+      <c r="B144" t="s">
+        <v>426</v>
+      </c>
+      <c r="C144" t="s">
+        <v>427</v>
+      </c>
+    </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A145" t="s">
+        <v>428</v>
+      </c>
+      <c r="B145" t="s">
+        <v>429</v>
+      </c>
+      <c r="C145" t="s">
+        <v>430</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/compounds.xlsx
+++ b/compounds.xlsx
@@ -8,12 +8,13 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ef049bac3ee44fb5/デスクトップ/構造クイズ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="17" documentId="8_{D4CA0FFB-8ADF-409B-8EC3-E330B2D69C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC396342-1A80-4B1B-8D16-18AC9186294F}"/>
+  <xr:revisionPtr revIDLastSave="24" documentId="8_{D4CA0FFB-8ADF-409B-8EC3-E330B2D69C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC58DD6F-FFDD-4FDB-BE03-2BE4E2C1E3FC}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{60308777-13F3-4883-9DF9-D5C4FE3A0F3D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{60308777-13F3-4883-9DF9-D5C4FE3A0F3D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="434">
   <si>
     <t>structure</t>
   </si>
@@ -1208,18 +1209,12 @@
     <t>Sodium borohydride</t>
   </si>
   <si>
-    <t>CC(=O)O[B-](H)(OC(C)=O)OC(C)=O.[Na+]</t>
-  </si>
-  <si>
     <t>STAB</t>
   </si>
   <si>
     <t>Sodium triacetoxyborohydride</t>
   </si>
   <si>
-    <t>CCC(C)[B-](H)(C(C)CC)C(C)CC.[Li+]</t>
-  </si>
-  <si>
     <t>L-Selectride</t>
   </si>
   <si>
@@ -1316,22 +1311,38 @@
     <t>Corey-Bakshi-Shibata catalyst (Me-CBS)</t>
   </si>
   <si>
-    <t>Cc1cc(C)c(c(C)c1)N2C=[C]N(C2)c3c(C)cc(C)cc3C</t>
-  </si>
-  <si>
     <t>IMes</t>
   </si>
   <si>
     <t>1,3-Bis(2,4,6-trimethylphenyl)imidazol-2-ylidene</t>
   </si>
   <si>
-    <t>CC(C)c1cccc(C(C)C)c1N2C=[C]N(C2)c3c(C(C)C)cccc3C(C)C</t>
-  </si>
-  <si>
     <t>IPr</t>
   </si>
   <si>
     <t>1,3-Bis(2,6-diisopropylphenyl)imidazol-2-ylidene</t>
+  </si>
+  <si>
+    <t>CC(=O)O[BH-](OC(C)=O)OC(C)=O.[Na+]</t>
+  </si>
+  <si>
+    <t>CCC(C)[BH-](C(C)CC)C(C)CC.[Li+]</t>
+  </si>
+  <si>
+    <t>Cc1cc(C)c(c(C)c1)N2C=C[C]N2c3c(C)cc(C)cc3C</t>
+  </si>
+  <si>
+    <t>CC(C)c1cccc(C(C)C)c1N2C=C[C]N2c3c(C(C)C)cccc3C(C)C</t>
+  </si>
+  <si>
+    <t>c1ccc(P(c2ccccc2)C3=CC=C[CH-]3)cc1.c4ccc(P(c5ccccc5)C6=CC=C[CH-]6)cc4.[Fe+2]</t>
+  </si>
+  <si>
+    <t>C1=CC=NC(=C1)C2=CC=CC=N2.C1=CC=NC(=C1)C2=CC=CC=N2.C1=CC=NC(=C1)C2=CC=CC=N2.[Ru+2]</t>
+  </si>
+  <si>
+    <t>Cc1cc(C)c(c(C)c1)N2C=C[C]N2c3c(C)cc(C)cc3C</t>
+    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -3184,156 +3195,233 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
+        <v>427</v>
+      </c>
+      <c r="B132" t="s">
         <v>389</v>
       </c>
-      <c r="B132" t="s">
+      <c r="C132" t="s">
         <v>390</v>
-      </c>
-      <c r="C132" t="s">
-        <v>391</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
+        <v>428</v>
+      </c>
+      <c r="B133" t="s">
+        <v>391</v>
+      </c>
+      <c r="C133" t="s">
         <v>392</v>
-      </c>
-      <c r="B133" t="s">
-        <v>393</v>
-      </c>
-      <c r="C133" t="s">
-        <v>394</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
+        <v>393</v>
+      </c>
+      <c r="B134" t="s">
+        <v>394</v>
+      </c>
+      <c r="C134" t="s">
         <v>395</v>
-      </c>
-      <c r="B134" t="s">
-        <v>396</v>
-      </c>
-      <c r="C134" t="s">
-        <v>397</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
+        <v>396</v>
+      </c>
+      <c r="B135" t="s">
+        <v>397</v>
+      </c>
+      <c r="C135" t="s">
         <v>398</v>
-      </c>
-      <c r="B135" t="s">
-        <v>399</v>
-      </c>
-      <c r="C135" t="s">
-        <v>400</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
+        <v>399</v>
+      </c>
+      <c r="B136" t="s">
+        <v>400</v>
+      </c>
+      <c r="C136" t="s">
         <v>401</v>
-      </c>
-      <c r="B136" t="s">
-        <v>402</v>
-      </c>
-      <c r="C136" t="s">
-        <v>403</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
+        <v>402</v>
+      </c>
+      <c r="B137" t="s">
+        <v>403</v>
+      </c>
+      <c r="C137" t="s">
         <v>404</v>
-      </c>
-      <c r="B137" t="s">
-        <v>405</v>
-      </c>
-      <c r="C137" t="s">
-        <v>406</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
+        <v>405</v>
+      </c>
+      <c r="B138" t="s">
+        <v>406</v>
+      </c>
+      <c r="C138" t="s">
         <v>407</v>
-      </c>
-      <c r="B138" t="s">
-        <v>408</v>
-      </c>
-      <c r="C138" t="s">
-        <v>409</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
+        <v>408</v>
+      </c>
+      <c r="B139" t="s">
+        <v>409</v>
+      </c>
+      <c r="C139" t="s">
         <v>410</v>
-      </c>
-      <c r="B139" t="s">
-        <v>411</v>
-      </c>
-      <c r="C139" t="s">
-        <v>412</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
+        <v>411</v>
+      </c>
+      <c r="B140" t="s">
+        <v>412</v>
+      </c>
+      <c r="C140" t="s">
         <v>413</v>
-      </c>
-      <c r="B140" t="s">
-        <v>414</v>
-      </c>
-      <c r="C140" t="s">
-        <v>415</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
+        <v>414</v>
+      </c>
+      <c r="B141" t="s">
+        <v>415</v>
+      </c>
+      <c r="C141" t="s">
         <v>416</v>
-      </c>
-      <c r="B141" t="s">
-        <v>417</v>
-      </c>
-      <c r="C141" t="s">
-        <v>418</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
+        <v>417</v>
+      </c>
+      <c r="B142" t="s">
+        <v>418</v>
+      </c>
+      <c r="C142" t="s">
         <v>419</v>
-      </c>
-      <c r="B142" t="s">
-        <v>420</v>
-      </c>
-      <c r="C142" t="s">
-        <v>421</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
+        <v>420</v>
+      </c>
+      <c r="B143" t="s">
+        <v>421</v>
+      </c>
+      <c r="C143" t="s">
         <v>422</v>
-      </c>
-      <c r="B143" t="s">
-        <v>423</v>
-      </c>
-      <c r="C143" t="s">
-        <v>424</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
-        <v>425</v>
+        <v>429</v>
       </c>
       <c r="B144" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
       <c r="C144" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
+        <v>430</v>
+      </c>
+      <c r="B145" t="s">
+        <v>425</v>
+      </c>
+      <c r="C145" t="s">
+        <v>426</v>
+      </c>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7F1A402-705D-487A-81AA-C034979C64E1}">
+  <dimension ref="A1:C6"/>
+  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
+  <sheetData>
+    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A1" t="s">
+        <v>427</v>
+      </c>
+      <c r="B1" t="s">
+        <v>389</v>
+      </c>
+      <c r="C1" t="s">
+        <v>390</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A2" t="s">
         <v>428</v>
       </c>
-      <c r="B145" t="s">
-        <v>429</v>
-      </c>
-      <c r="C145" t="s">
+      <c r="B2" t="s">
+        <v>391</v>
+      </c>
+      <c r="C2" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A3" t="s">
+        <v>433</v>
+      </c>
+      <c r="B3" t="s">
+        <v>423</v>
+      </c>
+      <c r="C3" t="s">
+        <v>424</v>
+      </c>
+    </row>
+    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A4" t="s">
         <v>430</v>
+      </c>
+      <c r="B4" t="s">
+        <v>425</v>
+      </c>
+      <c r="C4" t="s">
+        <v>426</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A5" t="s">
+        <v>431</v>
+      </c>
+      <c r="B5" t="s">
+        <v>336</v>
+      </c>
+      <c r="C5" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A6" t="s">
+        <v>432</v>
+      </c>
+      <c r="B6" t="s">
+        <v>342</v>
+      </c>
+      <c r="C6" t="s">
+        <v>343</v>
       </c>
     </row>
   </sheetData>

--- a/compounds.xlsx
+++ b/compounds.xlsx
@@ -8,13 +8,12 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ef049bac3ee44fb5/デスクトップ/構造クイズ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="24" documentId="8_{D4CA0FFB-8ADF-409B-8EC3-E330B2D69C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC58DD6F-FFDD-4FDB-BE03-2BE4E2C1E3FC}"/>
+  <xr:revisionPtr revIDLastSave="25" documentId="8_{D4CA0FFB-8ADF-409B-8EC3-E330B2D69C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D7821A7-1300-4378-96EA-E0DB5C4DFF50}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" activeTab="1" xr2:uid="{60308777-13F3-4883-9DF9-D5C4FE3A0F3D}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{60308777-13F3-4883-9DF9-D5C4FE3A0F3D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="453" uniqueCount="434">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="431">
   <si>
     <t>structure</t>
   </si>
@@ -1333,16 +1332,6 @@
   </si>
   <si>
     <t>CC(C)c1cccc(C(C)C)c1N2C=C[C]N2c3c(C(C)C)cccc3C(C)C</t>
-  </si>
-  <si>
-    <t>c1ccc(P(c2ccccc2)C3=CC=C[CH-]3)cc1.c4ccc(P(c5ccccc5)C6=CC=C[CH-]6)cc4.[Fe+2]</t>
-  </si>
-  <si>
-    <t>C1=CC=NC(=C1)C2=CC=CC=N2.C1=CC=NC(=C1)C2=CC=CC=N2.C1=CC=NC(=C1)C2=CC=CC=N2.[Ru+2]</t>
-  </si>
-  <si>
-    <t>Cc1cc(C)c(c(C)c1)N2C=C[C]N2c3c(C)cc(C)cc3C</t>
-    <phoneticPr fontId="1"/>
   </si>
 </sst>
 </file>
@@ -3351,81 +3340,4 @@
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7F1A402-705D-487A-81AA-C034979C64E1}">
-  <dimension ref="A1:C6"/>
-  <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
-  <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A1" t="s">
-        <v>427</v>
-      </c>
-      <c r="B1" t="s">
-        <v>389</v>
-      </c>
-      <c r="C1" t="s">
-        <v>390</v>
-      </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A2" t="s">
-        <v>428</v>
-      </c>
-      <c r="B2" t="s">
-        <v>391</v>
-      </c>
-      <c r="C2" t="s">
-        <v>392</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A3" t="s">
-        <v>433</v>
-      </c>
-      <c r="B3" t="s">
-        <v>423</v>
-      </c>
-      <c r="C3" t="s">
-        <v>424</v>
-      </c>
-    </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A4" t="s">
-        <v>430</v>
-      </c>
-      <c r="B4" t="s">
-        <v>425</v>
-      </c>
-      <c r="C4" t="s">
-        <v>426</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A5" t="s">
-        <v>431</v>
-      </c>
-      <c r="B5" t="s">
-        <v>336</v>
-      </c>
-      <c r="C5" t="s">
-        <v>337</v>
-      </c>
-    </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A6" t="s">
-        <v>432</v>
-      </c>
-      <c r="B6" t="s">
-        <v>342</v>
-      </c>
-      <c r="C6" t="s">
-        <v>343</v>
-      </c>
-    </row>
-  </sheetData>
-  <phoneticPr fontId="1"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
 </file>
--- a/compounds.xlsx
+++ b/compounds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ef049bac3ee44fb5/デスクトップ/構造クイズ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="25" documentId="8_{D4CA0FFB-8ADF-409B-8EC3-E330B2D69C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9D7821A7-1300-4378-96EA-E0DB5C4DFF50}"/>
+  <xr:revisionPtr revIDLastSave="31" documentId="8_{D4CA0FFB-8ADF-409B-8EC3-E330B2D69C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C29950CD-F1C6-4E27-B5B6-36F5BD31077A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{60308777-13F3-4883-9DF9-D5C4FE3A0F3D}"/>
   </bookViews>
@@ -638,9 +638,6 @@
     <t>Dimethyl sulfoxide</t>
   </si>
   <si>
-    <t>CC1C2CC(C2(C)C)C1B(H)C3CC4CC(C3C)C4(C)C</t>
-  </si>
-  <si>
     <t>DIPC</t>
   </si>
   <si>
@@ -800,9 +797,6 @@
     <t>N-Methyl-2-pyrrolidone</t>
   </si>
   <si>
-    <t>c1ccc2c(c1)-c1nc3nc(nc4[nH]c(nc5nc(nc([nH]1)c2)c1ccccc51)c1ccccc41)c1ccccc31</t>
-  </si>
-  <si>
     <t>Pc</t>
   </si>
   <si>
@@ -1082,9 +1076,6 @@
     <t>9,10-Dicyanoanthracene</t>
   </si>
   <si>
-    <t>N#Cc1c(N2c3ccccc3c4ccccc24)c(C#N)c(N5c6ccccc6c7ccccc57)c(N8c9ccccc9c10ccccc810)c1(N11c12ccccc12c13ccccc1113)</t>
-  </si>
-  <si>
     <t>4-CzIPN</t>
   </si>
   <si>
@@ -1332,6 +1323,15 @@
   </si>
   <si>
     <t>CC(C)c1cccc(C(C)C)c1N2C=C[C]N2c3c(C(C)C)cccc3C(C)C</t>
+  </si>
+  <si>
+    <t>CC1(C)C2CC[C@@H](C1)[C@H](C2)[BH][C@H]3[C@@H]4CC[C@](C)(C4)C3(C)C</t>
+  </si>
+  <si>
+    <t>c1ccc2c(c1)c3nc4nc(nc5c6ccccc6c(nc7nc(nc2n3)c8ccccc78)n5)[nH]c4[nH]</t>
+  </si>
+  <si>
+    <t>N#Cc1c(N2c3ccccc3c4ccccc24)c(C#N)c(N3c4ccccc4c5ccccc35)c(N4c5ccccc5c6ccccc46)c1N5c6ccccc6c7ccccc57</t>
   </si>
 </sst>
 </file>
@@ -1415,10 +1415,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2480,860 +2476,860 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
+        <v>428</v>
+      </c>
+      <c r="B68" t="s">
         <v>199</v>
       </c>
-      <c r="B68" t="s">
+      <c r="C68" t="s">
         <v>200</v>
-      </c>
-      <c r="C68" t="s">
-        <v>201</v>
       </c>
     </row>
     <row r="69" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A69" t="s">
+        <v>201</v>
+      </c>
+      <c r="B69" t="s">
         <v>202</v>
       </c>
-      <c r="B69" t="s">
+      <c r="C69" t="s">
         <v>203</v>
-      </c>
-      <c r="C69" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="70" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A70" t="s">
+        <v>204</v>
+      </c>
+      <c r="B70" t="s">
         <v>205</v>
       </c>
-      <c r="B70" t="s">
+      <c r="C70" t="s">
         <v>206</v>
-      </c>
-      <c r="C70" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="71" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A71" t="s">
+        <v>207</v>
+      </c>
+      <c r="B71" t="s">
         <v>208</v>
       </c>
-      <c r="B71" t="s">
+      <c r="C71" t="s">
         <v>209</v>
-      </c>
-      <c r="C71" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="72" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A72" t="s">
+        <v>210</v>
+      </c>
+      <c r="B72" t="s">
         <v>211</v>
       </c>
-      <c r="B72" t="s">
+      <c r="C72" t="s">
         <v>212</v>
-      </c>
-      <c r="C72" t="s">
-        <v>213</v>
       </c>
     </row>
     <row r="73" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A73" t="s">
+        <v>213</v>
+      </c>
+      <c r="B73" t="s">
         <v>214</v>
       </c>
-      <c r="B73" t="s">
+      <c r="C73" t="s">
         <v>215</v>
-      </c>
-      <c r="C73" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="74" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A74" t="s">
+        <v>216</v>
+      </c>
+      <c r="B74" t="s">
         <v>217</v>
       </c>
-      <c r="B74" t="s">
+      <c r="C74" t="s">
         <v>218</v>
-      </c>
-      <c r="C74" t="s">
-        <v>219</v>
       </c>
     </row>
     <row r="75" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A75" t="s">
+        <v>219</v>
+      </c>
+      <c r="B75" t="s">
         <v>220</v>
       </c>
-      <c r="B75" t="s">
+      <c r="C75" t="s">
         <v>221</v>
-      </c>
-      <c r="C75" t="s">
-        <v>222</v>
       </c>
     </row>
     <row r="76" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A76" t="s">
+        <v>222</v>
+      </c>
+      <c r="B76" t="s">
         <v>223</v>
       </c>
-      <c r="B76" t="s">
+      <c r="C76" t="s">
         <v>224</v>
-      </c>
-      <c r="C76" t="s">
-        <v>225</v>
       </c>
     </row>
     <row r="77" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A77" t="s">
+        <v>225</v>
+      </c>
+      <c r="B77" t="s">
         <v>226</v>
       </c>
-      <c r="B77" t="s">
+      <c r="C77" t="s">
         <v>227</v>
-      </c>
-      <c r="C77" t="s">
-        <v>228</v>
       </c>
     </row>
     <row r="78" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A78" t="s">
+        <v>228</v>
+      </c>
+      <c r="B78" t="s">
         <v>229</v>
       </c>
-      <c r="B78" t="s">
+      <c r="C78" t="s">
         <v>230</v>
-      </c>
-      <c r="C78" t="s">
-        <v>231</v>
       </c>
     </row>
     <row r="79" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A79" t="s">
+        <v>231</v>
+      </c>
+      <c r="B79" t="s">
         <v>232</v>
       </c>
-      <c r="B79" t="s">
+      <c r="C79" t="s">
         <v>233</v>
-      </c>
-      <c r="C79" t="s">
-        <v>234</v>
       </c>
     </row>
     <row r="80" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A80" t="s">
+        <v>234</v>
+      </c>
+      <c r="B80" t="s">
         <v>235</v>
       </c>
-      <c r="B80" t="s">
+      <c r="C80" t="s">
         <v>236</v>
-      </c>
-      <c r="C80" t="s">
-        <v>237</v>
       </c>
     </row>
     <row r="81" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A81" t="s">
+        <v>237</v>
+      </c>
+      <c r="B81" t="s">
         <v>238</v>
       </c>
-      <c r="B81" t="s">
+      <c r="C81" t="s">
         <v>239</v>
-      </c>
-      <c r="C81" t="s">
-        <v>240</v>
       </c>
     </row>
     <row r="82" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A82" t="s">
+        <v>240</v>
+      </c>
+      <c r="B82" t="s">
         <v>241</v>
       </c>
-      <c r="B82" t="s">
+      <c r="C82" t="s">
         <v>242</v>
-      </c>
-      <c r="C82" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="83" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A83" t="s">
+        <v>243</v>
+      </c>
+      <c r="B83" t="s">
         <v>244</v>
       </c>
-      <c r="B83" t="s">
+      <c r="C83" t="s">
         <v>245</v>
-      </c>
-      <c r="C83" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="84" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A84" t="s">
+        <v>246</v>
+      </c>
+      <c r="B84" t="s">
         <v>247</v>
       </c>
-      <c r="B84" t="s">
+      <c r="C84" t="s">
         <v>248</v>
-      </c>
-      <c r="C84" t="s">
-        <v>249</v>
       </c>
     </row>
     <row r="85" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A85" t="s">
+        <v>249</v>
+      </c>
+      <c r="B85" t="s">
         <v>250</v>
       </c>
-      <c r="B85" t="s">
+      <c r="C85" t="s">
         <v>251</v>
-      </c>
-      <c r="C85" t="s">
-        <v>252</v>
       </c>
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
+        <v>429</v>
+      </c>
+      <c r="B86" t="s">
+        <v>252</v>
+      </c>
+      <c r="C86" t="s">
         <v>253</v>
-      </c>
-      <c r="B86" t="s">
-        <v>254</v>
-      </c>
-      <c r="C86" t="s">
-        <v>255</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
+        <v>254</v>
+      </c>
+      <c r="B87" t="s">
+        <v>255</v>
+      </c>
+      <c r="C87" t="s">
         <v>256</v>
-      </c>
-      <c r="B87" t="s">
-        <v>257</v>
-      </c>
-      <c r="C87" t="s">
-        <v>258</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
+        <v>257</v>
+      </c>
+      <c r="B88" t="s">
+        <v>258</v>
+      </c>
+      <c r="C88" t="s">
         <v>259</v>
-      </c>
-      <c r="B88" t="s">
-        <v>260</v>
-      </c>
-      <c r="C88" t="s">
-        <v>261</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
+        <v>260</v>
+      </c>
+      <c r="B89" t="s">
+        <v>261</v>
+      </c>
+      <c r="C89" t="s">
         <v>262</v>
-      </c>
-      <c r="B89" t="s">
-        <v>263</v>
-      </c>
-      <c r="C89" t="s">
-        <v>264</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
+        <v>263</v>
+      </c>
+      <c r="B90" t="s">
+        <v>264</v>
+      </c>
+      <c r="C90" t="s">
         <v>265</v>
-      </c>
-      <c r="B90" t="s">
-        <v>266</v>
-      </c>
-      <c r="C90" t="s">
-        <v>267</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
+        <v>266</v>
+      </c>
+      <c r="B91" t="s">
+        <v>267</v>
+      </c>
+      <c r="C91" t="s">
         <v>268</v>
-      </c>
-      <c r="B91" t="s">
-        <v>269</v>
-      </c>
-      <c r="C91" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
+        <v>269</v>
+      </c>
+      <c r="B92" t="s">
+        <v>270</v>
+      </c>
+      <c r="C92" t="s">
         <v>271</v>
-      </c>
-      <c r="B92" t="s">
-        <v>272</v>
-      </c>
-      <c r="C92" t="s">
-        <v>273</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
+        <v>272</v>
+      </c>
+      <c r="B93" t="s">
+        <v>273</v>
+      </c>
+      <c r="C93" t="s">
         <v>274</v>
-      </c>
-      <c r="B93" t="s">
-        <v>275</v>
-      </c>
-      <c r="C93" t="s">
-        <v>276</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
+        <v>275</v>
+      </c>
+      <c r="B94" t="s">
+        <v>276</v>
+      </c>
+      <c r="C94" t="s">
         <v>277</v>
-      </c>
-      <c r="B94" t="s">
-        <v>278</v>
-      </c>
-      <c r="C94" t="s">
-        <v>279</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
+        <v>278</v>
+      </c>
+      <c r="B95" t="s">
+        <v>279</v>
+      </c>
+      <c r="C95" t="s">
         <v>280</v>
-      </c>
-      <c r="B95" t="s">
-        <v>281</v>
-      </c>
-      <c r="C95" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
+        <v>281</v>
+      </c>
+      <c r="B96" t="s">
+        <v>282</v>
+      </c>
+      <c r="C96" t="s">
         <v>283</v>
-      </c>
-      <c r="B96" t="s">
-        <v>284</v>
-      </c>
-      <c r="C96" t="s">
-        <v>285</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
+        <v>284</v>
+      </c>
+      <c r="B97" t="s">
+        <v>285</v>
+      </c>
+      <c r="C97" t="s">
         <v>286</v>
-      </c>
-      <c r="B97" t="s">
-        <v>287</v>
-      </c>
-      <c r="C97" t="s">
-        <v>288</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
+        <v>287</v>
+      </c>
+      <c r="B98" t="s">
+        <v>288</v>
+      </c>
+      <c r="C98" t="s">
         <v>289</v>
-      </c>
-      <c r="B98" t="s">
-        <v>290</v>
-      </c>
-      <c r="C98" t="s">
-        <v>291</v>
       </c>
     </row>
     <row r="99" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A99" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="B99" t="s">
         <v>104</v>
       </c>
       <c r="C99" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
+        <v>292</v>
+      </c>
+      <c r="B100" t="s">
+        <v>293</v>
+      </c>
+      <c r="C100" t="s">
         <v>294</v>
-      </c>
-      <c r="B100" t="s">
-        <v>295</v>
-      </c>
-      <c r="C100" t="s">
-        <v>296</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
+        <v>295</v>
+      </c>
+      <c r="B101" t="s">
+        <v>296</v>
+      </c>
+      <c r="C101" t="s">
         <v>297</v>
-      </c>
-      <c r="B101" t="s">
-        <v>298</v>
-      </c>
-      <c r="C101" t="s">
-        <v>299</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
+        <v>298</v>
+      </c>
+      <c r="B102" t="s">
+        <v>299</v>
+      </c>
+      <c r="C102" t="s">
         <v>300</v>
-      </c>
-      <c r="B102" t="s">
-        <v>301</v>
-      </c>
-      <c r="C102" t="s">
-        <v>302</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
+        <v>301</v>
+      </c>
+      <c r="B103" t="s">
+        <v>302</v>
+      </c>
+      <c r="C103" t="s">
         <v>303</v>
-      </c>
-      <c r="B103" t="s">
-        <v>304</v>
-      </c>
-      <c r="C103" t="s">
-        <v>305</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
+        <v>304</v>
+      </c>
+      <c r="B104" t="s">
+        <v>305</v>
+      </c>
+      <c r="C104" t="s">
         <v>306</v>
-      </c>
-      <c r="B104" t="s">
-        <v>307</v>
-      </c>
-      <c r="C104" t="s">
-        <v>308</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
+        <v>307</v>
+      </c>
+      <c r="B105" t="s">
+        <v>308</v>
+      </c>
+      <c r="C105" t="s">
         <v>309</v>
-      </c>
-      <c r="B105" t="s">
-        <v>310</v>
-      </c>
-      <c r="C105" t="s">
-        <v>311</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
+        <v>310</v>
+      </c>
+      <c r="B106" t="s">
+        <v>311</v>
+      </c>
+      <c r="C106" t="s">
         <v>312</v>
-      </c>
-      <c r="B106" t="s">
-        <v>313</v>
-      </c>
-      <c r="C106" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
+        <v>313</v>
+      </c>
+      <c r="B107" t="s">
+        <v>314</v>
+      </c>
+      <c r="C107" t="s">
         <v>315</v>
-      </c>
-      <c r="B107" t="s">
-        <v>316</v>
-      </c>
-      <c r="C107" t="s">
-        <v>317</v>
       </c>
     </row>
     <row r="108" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A108" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B108" t="s">
         <v>110</v>
       </c>
       <c r="C108" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
+        <v>318</v>
+      </c>
+      <c r="B109" t="s">
+        <v>319</v>
+      </c>
+      <c r="C109" t="s">
         <v>320</v>
-      </c>
-      <c r="B109" t="s">
-        <v>321</v>
-      </c>
-      <c r="C109" t="s">
-        <v>322</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
+        <v>321</v>
+      </c>
+      <c r="B110" t="s">
+        <v>322</v>
+      </c>
+      <c r="C110" t="s">
         <v>323</v>
-      </c>
-      <c r="B110" t="s">
-        <v>324</v>
-      </c>
-      <c r="C110" t="s">
-        <v>325</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
+        <v>324</v>
+      </c>
+      <c r="B111" t="s">
+        <v>325</v>
+      </c>
+      <c r="C111" t="s">
         <v>326</v>
-      </c>
-      <c r="B111" t="s">
-        <v>327</v>
-      </c>
-      <c r="C111" t="s">
-        <v>328</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
+        <v>327</v>
+      </c>
+      <c r="B112" t="s">
+        <v>328</v>
+      </c>
+      <c r="C112" t="s">
         <v>329</v>
-      </c>
-      <c r="B112" t="s">
-        <v>330</v>
-      </c>
-      <c r="C112" t="s">
-        <v>331</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
+        <v>330</v>
+      </c>
+      <c r="B113" t="s">
+        <v>331</v>
+      </c>
+      <c r="C113" t="s">
         <v>332</v>
-      </c>
-      <c r="B113" t="s">
-        <v>333</v>
-      </c>
-      <c r="C113" t="s">
-        <v>334</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
+        <v>333</v>
+      </c>
+      <c r="B114" t="s">
+        <v>334</v>
+      </c>
+      <c r="C114" t="s">
         <v>335</v>
-      </c>
-      <c r="B114" t="s">
-        <v>336</v>
-      </c>
-      <c r="C114" t="s">
-        <v>337</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
+        <v>336</v>
+      </c>
+      <c r="B115" t="s">
+        <v>337</v>
+      </c>
+      <c r="C115" t="s">
         <v>338</v>
-      </c>
-      <c r="B115" t="s">
-        <v>339</v>
-      </c>
-      <c r="C115" t="s">
-        <v>340</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
+        <v>339</v>
+      </c>
+      <c r="B116" t="s">
+        <v>340</v>
+      </c>
+      <c r="C116" t="s">
         <v>341</v>
-      </c>
-      <c r="B116" t="s">
-        <v>342</v>
-      </c>
-      <c r="C116" t="s">
-        <v>343</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
+        <v>342</v>
+      </c>
+      <c r="B117" t="s">
+        <v>343</v>
+      </c>
+      <c r="C117" t="s">
         <v>344</v>
-      </c>
-      <c r="B117" t="s">
-        <v>345</v>
-      </c>
-      <c r="C117" t="s">
-        <v>346</v>
       </c>
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
-        <v>347</v>
+        <v>430</v>
       </c>
       <c r="B118" t="s">
-        <v>348</v>
+        <v>345</v>
       </c>
       <c r="C118" t="s">
-        <v>349</v>
+        <v>346</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
-        <v>350</v>
+        <v>347</v>
       </c>
       <c r="B119" t="s">
-        <v>351</v>
+        <v>348</v>
       </c>
       <c r="C119" t="s">
-        <v>352</v>
+        <v>349</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
-        <v>353</v>
+        <v>350</v>
       </c>
       <c r="B120" t="s">
-        <v>354</v>
+        <v>351</v>
       </c>
       <c r="C120" t="s">
-        <v>355</v>
+        <v>352</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
-        <v>356</v>
+        <v>353</v>
       </c>
       <c r="B121" t="s">
-        <v>357</v>
+        <v>354</v>
       </c>
       <c r="C121" t="s">
-        <v>358</v>
+        <v>355</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
-        <v>359</v>
+        <v>356</v>
       </c>
       <c r="B122" t="s">
-        <v>360</v>
+        <v>357</v>
       </c>
       <c r="C122" t="s">
-        <v>361</v>
+        <v>358</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
-        <v>362</v>
+        <v>359</v>
       </c>
       <c r="B123" t="s">
-        <v>363</v>
+        <v>360</v>
       </c>
       <c r="C123" t="s">
-        <v>364</v>
+        <v>361</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
-        <v>365</v>
+        <v>362</v>
       </c>
       <c r="B124" t="s">
-        <v>366</v>
+        <v>363</v>
       </c>
       <c r="C124" t="s">
-        <v>367</v>
+        <v>364</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
-        <v>368</v>
+        <v>365</v>
       </c>
       <c r="B125" t="s">
-        <v>369</v>
+        <v>366</v>
       </c>
       <c r="C125" t="s">
-        <v>370</v>
+        <v>367</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
-        <v>371</v>
+        <v>368</v>
       </c>
       <c r="B126" t="s">
-        <v>372</v>
+        <v>369</v>
       </c>
       <c r="C126" t="s">
-        <v>373</v>
+        <v>370</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
-        <v>374</v>
+        <v>371</v>
       </c>
       <c r="B127" t="s">
-        <v>375</v>
+        <v>372</v>
       </c>
       <c r="C127" t="s">
-        <v>376</v>
+        <v>373</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
-        <v>377</v>
+        <v>374</v>
       </c>
       <c r="B128" t="s">
-        <v>378</v>
+        <v>375</v>
       </c>
       <c r="C128" t="s">
-        <v>379</v>
+        <v>376</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
-        <v>380</v>
+        <v>377</v>
       </c>
       <c r="B129" t="s">
-        <v>381</v>
+        <v>378</v>
       </c>
       <c r="C129" t="s">
-        <v>382</v>
+        <v>379</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
-        <v>383</v>
+        <v>380</v>
       </c>
       <c r="B130" t="s">
-        <v>384</v>
+        <v>381</v>
       </c>
       <c r="C130" t="s">
-        <v>385</v>
+        <v>382</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
-        <v>386</v>
+        <v>383</v>
       </c>
       <c r="B131" t="s">
-        <v>387</v>
+        <v>384</v>
       </c>
       <c r="C131" t="s">
-        <v>388</v>
+        <v>385</v>
       </c>
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
-        <v>427</v>
+        <v>424</v>
       </c>
       <c r="B132" t="s">
-        <v>389</v>
+        <v>386</v>
       </c>
       <c r="C132" t="s">
-        <v>390</v>
+        <v>387</v>
       </c>
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
-        <v>428</v>
+        <v>425</v>
       </c>
       <c r="B133" t="s">
-        <v>391</v>
+        <v>388</v>
       </c>
       <c r="C133" t="s">
-        <v>392</v>
+        <v>389</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
-        <v>393</v>
+        <v>390</v>
       </c>
       <c r="B134" t="s">
-        <v>394</v>
+        <v>391</v>
       </c>
       <c r="C134" t="s">
-        <v>395</v>
+        <v>392</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
-        <v>396</v>
+        <v>393</v>
       </c>
       <c r="B135" t="s">
-        <v>397</v>
+        <v>394</v>
       </c>
       <c r="C135" t="s">
-        <v>398</v>
+        <v>395</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
-        <v>399</v>
+        <v>396</v>
       </c>
       <c r="B136" t="s">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="C136" t="s">
-        <v>401</v>
+        <v>398</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
-        <v>402</v>
+        <v>399</v>
       </c>
       <c r="B137" t="s">
-        <v>403</v>
+        <v>400</v>
       </c>
       <c r="C137" t="s">
-        <v>404</v>
+        <v>401</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
-        <v>405</v>
+        <v>402</v>
       </c>
       <c r="B138" t="s">
-        <v>406</v>
+        <v>403</v>
       </c>
       <c r="C138" t="s">
-        <v>407</v>
+        <v>404</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
-        <v>408</v>
+        <v>405</v>
       </c>
       <c r="B139" t="s">
-        <v>409</v>
+        <v>406</v>
       </c>
       <c r="C139" t="s">
-        <v>410</v>
+        <v>407</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
-        <v>411</v>
+        <v>408</v>
       </c>
       <c r="B140" t="s">
-        <v>412</v>
+        <v>409</v>
       </c>
       <c r="C140" t="s">
-        <v>413</v>
+        <v>410</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
-        <v>414</v>
+        <v>411</v>
       </c>
       <c r="B141" t="s">
-        <v>415</v>
+        <v>412</v>
       </c>
       <c r="C141" t="s">
-        <v>416</v>
+        <v>413</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
-        <v>417</v>
+        <v>414</v>
       </c>
       <c r="B142" t="s">
-        <v>418</v>
+        <v>415</v>
       </c>
       <c r="C142" t="s">
-        <v>419</v>
+        <v>416</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
-        <v>420</v>
+        <v>417</v>
       </c>
       <c r="B143" t="s">
-        <v>421</v>
+        <v>418</v>
       </c>
       <c r="C143" t="s">
-        <v>422</v>
+        <v>419</v>
       </c>
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
-        <v>429</v>
+        <v>426</v>
       </c>
       <c r="B144" t="s">
-        <v>423</v>
+        <v>420</v>
       </c>
       <c r="C144" t="s">
-        <v>424</v>
+        <v>421</v>
       </c>
     </row>
     <row r="145" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A145" t="s">
-        <v>430</v>
+        <v>427</v>
       </c>
       <c r="B145" t="s">
-        <v>425</v>
+        <v>422</v>
       </c>
       <c r="C145" t="s">
-        <v>426</v>
+        <v>423</v>
       </c>
     </row>
   </sheetData>

--- a/compounds.xlsx
+++ b/compounds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ef049bac3ee44fb5/デスクトップ/構造クイズ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="31" documentId="8_{D4CA0FFB-8ADF-409B-8EC3-E330B2D69C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C29950CD-F1C6-4E27-B5B6-36F5BD31077A}"/>
+  <xr:revisionPtr revIDLastSave="32" documentId="8_{D4CA0FFB-8ADF-409B-8EC3-E330B2D69C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2F34994-732B-4658-9DC1-4E740A91B14A}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{60308777-13F3-4883-9DF9-D5C4FE3A0F3D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="435" uniqueCount="431">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="428">
   <si>
     <t>structure</t>
   </si>
@@ -797,12 +797,6 @@
     <t>N-Methyl-2-pyrrolidone</t>
   </si>
   <si>
-    <t>Pc</t>
-  </si>
-  <si>
-    <t>Phthalocyanine</t>
-  </si>
-  <si>
     <t>c1cc[nH+]cc1.[O-][Cr](Cl)(=O)=O</t>
   </si>
   <si>
@@ -1326,9 +1320,6 @@
   </si>
   <si>
     <t>CC1(C)C2CC[C@@H](C1)[C@H](C2)[BH][C@H]3[C@@H]4CC[C@](C)(C4)C3(C)C</t>
-  </si>
-  <si>
-    <t>c1ccc2c(c1)c3nc4nc(nc5c6ccccc6c(nc7nc(nc2n3)c8ccccc78)n5)[nH]c4[nH]</t>
   </si>
   <si>
     <t>N#Cc1c(N2c3ccccc3c4ccccc24)c(C#N)c(N3c4ccccc4c5ccccc35)c(N4c5ccccc5c6ccccc46)c1N5c6ccccc6c7ccccc57</t>
@@ -1415,6 +1406,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1734,7 +1729,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A2CED0-FCDE-4C58-8502-7B6BD1A44430}">
-  <dimension ref="A1:C145"/>
+  <dimension ref="A1:C144"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -2476,7 +2471,7 @@
     </row>
     <row r="68" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A68" t="s">
-        <v>428</v>
+        <v>426</v>
       </c>
       <c r="B68" t="s">
         <v>199</v>
@@ -2674,142 +2669,142 @@
     </row>
     <row r="86" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A86" t="s">
-        <v>429</v>
+        <v>252</v>
       </c>
       <c r="B86" t="s">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C86" t="s">
-        <v>253</v>
+        <v>254</v>
       </c>
     </row>
     <row r="87" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A87" t="s">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="B87" t="s">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="C87" t="s">
-        <v>256</v>
+        <v>257</v>
       </c>
     </row>
     <row r="88" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A88" t="s">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="B88" t="s">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="C88" t="s">
-        <v>259</v>
+        <v>260</v>
       </c>
     </row>
     <row r="89" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A89" t="s">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="B89" t="s">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C89" t="s">
-        <v>262</v>
+        <v>263</v>
       </c>
     </row>
     <row r="90" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A90" t="s">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="B90" t="s">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="C90" t="s">
-        <v>265</v>
+        <v>266</v>
       </c>
     </row>
     <row r="91" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A91" t="s">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="B91" t="s">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="C91" t="s">
-        <v>268</v>
+        <v>269</v>
       </c>
     </row>
     <row r="92" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A92" t="s">
-        <v>269</v>
+        <v>270</v>
       </c>
       <c r="B92" t="s">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C92" t="s">
-        <v>271</v>
+        <v>272</v>
       </c>
     </row>
     <row r="93" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A93" t="s">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="B93" t="s">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="C93" t="s">
-        <v>274</v>
+        <v>275</v>
       </c>
     </row>
     <row r="94" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A94" t="s">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="B94" t="s">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C94" t="s">
-        <v>277</v>
+        <v>278</v>
       </c>
     </row>
     <row r="95" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A95" t="s">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="B95" t="s">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="C95" t="s">
-        <v>280</v>
+        <v>281</v>
       </c>
     </row>
     <row r="96" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A96" t="s">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="B96" t="s">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C96" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
     </row>
     <row r="97" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A97" t="s">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B97" t="s">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C97" t="s">
-        <v>286</v>
+        <v>287</v>
       </c>
     </row>
     <row r="98" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A98" t="s">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="B98" t="s">
-        <v>288</v>
+        <v>104</v>
       </c>
       <c r="C98" t="s">
         <v>289</v>
@@ -2820,95 +2815,95 @@
         <v>290</v>
       </c>
       <c r="B99" t="s">
-        <v>104</v>
+        <v>291</v>
       </c>
       <c r="C99" t="s">
-        <v>291</v>
+        <v>292</v>
       </c>
     </row>
     <row r="100" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A100" t="s">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="B100" t="s">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="C100" t="s">
-        <v>294</v>
+        <v>295</v>
       </c>
     </row>
     <row r="101" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A101" t="s">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="B101" t="s">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="C101" t="s">
-        <v>297</v>
+        <v>298</v>
       </c>
     </row>
     <row r="102" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A102" t="s">
-        <v>298</v>
+        <v>299</v>
       </c>
       <c r="B102" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C102" t="s">
-        <v>300</v>
+        <v>301</v>
       </c>
     </row>
     <row r="103" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A103" t="s">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="B103" t="s">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="C103" t="s">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="104" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A104" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B104" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="C104" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
     </row>
     <row r="105" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A105" t="s">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B105" t="s">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="C105" t="s">
-        <v>309</v>
+        <v>310</v>
       </c>
     </row>
     <row r="106" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A106" t="s">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="B106" t="s">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="C106" t="s">
-        <v>312</v>
+        <v>313</v>
       </c>
     </row>
     <row r="107" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A107" t="s">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B107" t="s">
-        <v>314</v>
+        <v>110</v>
       </c>
       <c r="C107" t="s">
         <v>315</v>
@@ -2919,103 +2914,103 @@
         <v>316</v>
       </c>
       <c r="B108" t="s">
-        <v>110</v>
+        <v>317</v>
       </c>
       <c r="C108" t="s">
-        <v>317</v>
+        <v>318</v>
       </c>
     </row>
     <row r="109" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A109" t="s">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="B109" t="s">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="C109" t="s">
-        <v>320</v>
+        <v>321</v>
       </c>
     </row>
     <row r="110" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A110" t="s">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="B110" t="s">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="C110" t="s">
-        <v>323</v>
+        <v>324</v>
       </c>
     </row>
     <row r="111" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A111" t="s">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="B111" t="s">
-        <v>325</v>
+        <v>326</v>
       </c>
       <c r="C111" t="s">
-        <v>326</v>
+        <v>327</v>
       </c>
     </row>
     <row r="112" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A112" t="s">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="B112" t="s">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="C112" t="s">
-        <v>329</v>
+        <v>330</v>
       </c>
     </row>
     <row r="113" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A113" t="s">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B113" t="s">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C113" t="s">
-        <v>332</v>
+        <v>333</v>
       </c>
     </row>
     <row r="114" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A114" t="s">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="B114" t="s">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="C114" t="s">
-        <v>335</v>
+        <v>336</v>
       </c>
     </row>
     <row r="115" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A115" t="s">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="B115" t="s">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="C115" t="s">
-        <v>338</v>
+        <v>339</v>
       </c>
     </row>
     <row r="116" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A116" t="s">
-        <v>339</v>
+        <v>340</v>
       </c>
       <c r="B116" t="s">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="C116" t="s">
-        <v>341</v>
+        <v>342</v>
       </c>
     </row>
     <row r="117" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A117" t="s">
-        <v>342</v>
+        <v>427</v>
       </c>
       <c r="B117" t="s">
         <v>343</v>
@@ -3026,150 +3021,150 @@
     </row>
     <row r="118" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A118" t="s">
-        <v>430</v>
+        <v>345</v>
       </c>
       <c r="B118" t="s">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="C118" t="s">
-        <v>346</v>
+        <v>347</v>
       </c>
     </row>
     <row r="119" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A119" t="s">
-        <v>347</v>
+        <v>348</v>
       </c>
       <c r="B119" t="s">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="C119" t="s">
-        <v>349</v>
+        <v>350</v>
       </c>
     </row>
     <row r="120" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A120" t="s">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="B120" t="s">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="C120" t="s">
-        <v>352</v>
+        <v>353</v>
       </c>
     </row>
     <row r="121" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A121" t="s">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="B121" t="s">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="C121" t="s">
-        <v>355</v>
+        <v>356</v>
       </c>
     </row>
     <row r="122" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A122" t="s">
-        <v>356</v>
+        <v>357</v>
       </c>
       <c r="B122" t="s">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="C122" t="s">
-        <v>358</v>
+        <v>359</v>
       </c>
     </row>
     <row r="123" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A123" t="s">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="B123" t="s">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="C123" t="s">
-        <v>361</v>
+        <v>362</v>
       </c>
     </row>
     <row r="124" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A124" t="s">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="B124" t="s">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="C124" t="s">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="125" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A125" t="s">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B125" t="s">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C125" t="s">
-        <v>367</v>
+        <v>368</v>
       </c>
     </row>
     <row r="126" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A126" t="s">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="B126" t="s">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="C126" t="s">
-        <v>370</v>
+        <v>371</v>
       </c>
     </row>
     <row r="127" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A127" t="s">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="B127" t="s">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="C127" t="s">
-        <v>373</v>
+        <v>374</v>
       </c>
     </row>
     <row r="128" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A128" t="s">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="B128" t="s">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="C128" t="s">
-        <v>376</v>
+        <v>377</v>
       </c>
     </row>
     <row r="129" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A129" t="s">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="B129" t="s">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="C129" t="s">
-        <v>379</v>
+        <v>380</v>
       </c>
     </row>
     <row r="130" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A130" t="s">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="B130" t="s">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="C130" t="s">
-        <v>382</v>
+        <v>383</v>
       </c>
     </row>
     <row r="131" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A131" t="s">
-        <v>383</v>
+        <v>422</v>
       </c>
       <c r="B131" t="s">
         <v>384</v>
@@ -3180,7 +3175,7 @@
     </row>
     <row r="132" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A132" t="s">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="B132" t="s">
         <v>386</v>
@@ -3191,117 +3186,117 @@
     </row>
     <row r="133" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A133" t="s">
-        <v>425</v>
+        <v>388</v>
       </c>
       <c r="B133" t="s">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="C133" t="s">
-        <v>389</v>
+        <v>390</v>
       </c>
     </row>
     <row r="134" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A134" t="s">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B134" t="s">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="C134" t="s">
-        <v>392</v>
+        <v>393</v>
       </c>
     </row>
     <row r="135" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A135" t="s">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B135" t="s">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="C135" t="s">
-        <v>395</v>
+        <v>396</v>
       </c>
     </row>
     <row r="136" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A136" t="s">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B136" t="s">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="C136" t="s">
-        <v>398</v>
+        <v>399</v>
       </c>
     </row>
     <row r="137" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A137" t="s">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B137" t="s">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C137" t="s">
-        <v>401</v>
+        <v>402</v>
       </c>
     </row>
     <row r="138" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A138" t="s">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B138" t="s">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="C138" t="s">
-        <v>404</v>
+        <v>405</v>
       </c>
     </row>
     <row r="139" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A139" t="s">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B139" t="s">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C139" t="s">
-        <v>407</v>
+        <v>408</v>
       </c>
     </row>
     <row r="140" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A140" t="s">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="B140" t="s">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="C140" t="s">
-        <v>410</v>
+        <v>411</v>
       </c>
     </row>
     <row r="141" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A141" t="s">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B141" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C141" t="s">
-        <v>413</v>
+        <v>414</v>
       </c>
     </row>
     <row r="142" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A142" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="B142" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C142" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
     </row>
     <row r="143" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A143" t="s">
-        <v>417</v>
+        <v>424</v>
       </c>
       <c r="B143" t="s">
         <v>418</v>
@@ -3312,24 +3307,13 @@
     </row>
     <row r="144" spans="1:3" x14ac:dyDescent="0.55000000000000004">
       <c r="A144" t="s">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="B144" t="s">
         <v>420</v>
       </c>
       <c r="C144" t="s">
         <v>421</v>
-      </c>
-    </row>
-    <row r="145" spans="1:3" x14ac:dyDescent="0.55000000000000004">
-      <c r="A145" t="s">
-        <v>427</v>
-      </c>
-      <c r="B145" t="s">
-        <v>422</v>
-      </c>
-      <c r="C145" t="s">
-        <v>423</v>
       </c>
     </row>
   </sheetData>

--- a/compounds.xlsx
+++ b/compounds.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/ef049bac3ee44fb5/デスクトップ/構造クイズ/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="32" documentId="8_{D4CA0FFB-8ADF-409B-8EC3-E330B2D69C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A2F34994-732B-4658-9DC1-4E740A91B14A}"/>
+  <xr:revisionPtr revIDLastSave="42" documentId="8_{D4CA0FFB-8ADF-409B-8EC3-E330B2D69C5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{5EC03F77-BCD2-42B9-BFCD-4918AADE1399}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11500" xr2:uid="{60308777-13F3-4883-9DF9-D5C4FE3A0F3D}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="432" uniqueCount="428">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="504" uniqueCount="500">
   <si>
     <t>structure</t>
   </si>
@@ -1323,6 +1323,222 @@
   </si>
   <si>
     <t>N#Cc1c(N2c3ccccc3c4ccccc24)c(C#N)c(N3c4ccccc4c5ccccc35)c(N4c5ccccc5c6ccccc46)c1N5c6ccccc6c7ccccc57</t>
+  </si>
+  <si>
+    <t>CCCC[N+](CCCC)(CCCC)CCCC.F[Si-](F)(c1ccccc1)(c1ccccc1)c1ccccc1</t>
+  </si>
+  <si>
+    <t>TBAT</t>
+  </si>
+  <si>
+    <t>Tetrabutylammonium difluorotriphenylsilicate</t>
+  </si>
+  <si>
+    <t>*c1c(C)cc(C)cc1C</t>
+  </si>
+  <si>
+    <t>Mes</t>
+  </si>
+  <si>
+    <t>Mesityl</t>
+  </si>
+  <si>
+    <t>C(CP(c1ccccc1)c2ccccc2)P(c3ccccc3)c4ccccc4</t>
+  </si>
+  <si>
+    <t>dppe</t>
+  </si>
+  <si>
+    <t>1,2-Bis(diphenylphosphino)ethane</t>
+  </si>
+  <si>
+    <t>C(CCP(c1ccccc1)c2ccccc2)P(c3ccccc3)c4ccccc4</t>
+  </si>
+  <si>
+    <t>dppp</t>
+  </si>
+  <si>
+    <t>1,3-Bis(diphenylphosphino)propane</t>
+  </si>
+  <si>
+    <t>C(P(c1ccccc1)c2ccccc2)P(c3ccccc3)c4ccccc4</t>
+  </si>
+  <si>
+    <t>dppm</t>
+  </si>
+  <si>
+    <t>Bis(diphenylphosphino)methane</t>
+  </si>
+  <si>
+    <t>CC1(C)c2cccc(P(c3ccccc3)c4ccccc4)c2Oc5c1cccc5P(c6ccccc6)c7ccccc7</t>
+  </si>
+  <si>
+    <t>Xantphos</t>
+  </si>
+  <si>
+    <t>4,5-Bis(diphenylphosphino)-9,9-dimethylxanthene</t>
+  </si>
+  <si>
+    <t>c1ccc(nc1)-c2ccccn2</t>
+  </si>
+  <si>
+    <t>bipy</t>
+  </si>
+  <si>
+    <t>2,2'-Bipyridine</t>
+  </si>
+  <si>
+    <t>CC(C)(C)c1ccnc(c1)-c2cc(C(C)(C)C)ccn2</t>
+  </si>
+  <si>
+    <t>dtbbpy</t>
+  </si>
+  <si>
+    <t>4,4'-Di-tert-butyl-2,2'-bipyridine</t>
+  </si>
+  <si>
+    <t>[Li]C(C)(C)C</t>
+  </si>
+  <si>
+    <t>t-BuLi</t>
+  </si>
+  <si>
+    <t>tert-Butyllithium</t>
+  </si>
+  <si>
+    <t>CCC(C)[Li]</t>
+  </si>
+  <si>
+    <t>s-BuLi</t>
+  </si>
+  <si>
+    <t>sec-Butyllithium</t>
+  </si>
+  <si>
+    <t>CC1(C)C(C)(C)OB(B2OC(C)(C)C(C)(C)O2)O1</t>
+  </si>
+  <si>
+    <t>B2pin2</t>
+  </si>
+  <si>
+    <t>Bis(pinacolato)diboron</t>
+  </si>
+  <si>
+    <t>CC1(C)C(C)(C)O[BH]O1</t>
+  </si>
+  <si>
+    <t>HBpin</t>
+  </si>
+  <si>
+    <t>Pinacolborane</t>
+  </si>
+  <si>
+    <t>COc1cccc(OC)c1-c2ccccc2P(C3CCCCC3)C4CCCCC4</t>
+  </si>
+  <si>
+    <t>SPhos</t>
+  </si>
+  <si>
+    <t>2-Dicyclohexylphosphino-2',6'-dimethoxybiphenyl</t>
+  </si>
+  <si>
+    <t>CC(C)Oc1cccc(OC(C)C)c1-c2ccccc2P(C3CCCCC3)C4CCCCC4</t>
+  </si>
+  <si>
+    <t>RuPhos</t>
+  </si>
+  <si>
+    <t>2-Dicyclohexylphosphino-2',6'-diisopropoxybiphenyl</t>
+  </si>
+  <si>
+    <t>O(c1ccccc1P(c2ccccc2)c3ccccc3)c4ccccc4P(c5ccccc5)c6ccccc6</t>
+  </si>
+  <si>
+    <t>DPEphos</t>
+  </si>
+  <si>
+    <t>Bis(2-diphenylphosphinophenyl)ether</t>
+  </si>
+  <si>
+    <t>C[n+]1c2ccccc2c(c3c(C)cc(C)cc3C)c4ccccc14.[O-]Cl(=O)(=O)=O</t>
+  </si>
+  <si>
+    <t>Mes-Acr+</t>
+  </si>
+  <si>
+    <t>9-Mesityl-10-methylacridinium perchlorate</t>
+  </si>
+  <si>
+    <t>COc1ccc(P2(=S)SP(=S)(c3ccc(OC)cc3)S2)cc1</t>
+  </si>
+  <si>
+    <t>Lawesson's reagent</t>
+  </si>
+  <si>
+    <t>2,4-Bis(4-methoxyphenyl)-1,3,2,4-dithiadiphosphetane-2,4-dithione</t>
+  </si>
+  <si>
+    <t>O=P(Cl)(N1CCOC1=O)N2CCOC2=O</t>
+  </si>
+  <si>
+    <t>BOP-Cl</t>
+  </si>
+  <si>
+    <t>Bis(2-oxo-3-oxazolidinyl)phosphinic chloride</t>
+  </si>
+  <si>
+    <t>FC(F)(F)CO</t>
+  </si>
+  <si>
+    <t>TFE</t>
+  </si>
+  <si>
+    <t>2,2,2-Trifluoroethanol</t>
+  </si>
+  <si>
+    <t>ClCCCl</t>
+  </si>
+  <si>
+    <t>DCE</t>
+  </si>
+  <si>
+    <t>1,2-Dichloroethane</t>
+  </si>
+  <si>
+    <t>*c1cccc2ccccc12</t>
+  </si>
+  <si>
+    <t>Nap</t>
+  </si>
+  <si>
+    <t>1-Naphthyl</t>
+  </si>
+  <si>
+    <t>CC(C)[N-]C(C)C.[Li+]</t>
+  </si>
+  <si>
+    <t>LDA</t>
+  </si>
+  <si>
+    <t>Lithium diisopropylamide</t>
+  </si>
+  <si>
+    <t>c1ccncc1</t>
+  </si>
+  <si>
+    <t>Py</t>
+  </si>
+  <si>
+    <t>Pyridine</t>
+  </si>
+  <si>
+    <t>CCN(C(C)C)C(C)C</t>
+  </si>
+  <si>
+    <t>DIPEA</t>
+  </si>
+  <si>
+    <t>N,N-Diisopropylethylamine</t>
   </si>
 </sst>
 </file>
@@ -1406,10 +1622,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1729,7 +1941,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18A2CED0-FCDE-4C58-8502-7B6BD1A44430}">
-  <dimension ref="A1:C144"/>
+  <dimension ref="A1:C168"/>
   <sheetFormatPr defaultRowHeight="18" x14ac:dyDescent="0.55000000000000004"/>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.55000000000000004">
@@ -3316,6 +3528,270 @@
         <v>421</v>
       </c>
     </row>
+    <row r="145" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A145" t="s">
+        <v>428</v>
+      </c>
+      <c r="B145" t="s">
+        <v>429</v>
+      </c>
+      <c r="C145" t="s">
+        <v>430</v>
+      </c>
+    </row>
+    <row r="146" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A146" t="s">
+        <v>431</v>
+      </c>
+      <c r="B146" t="s">
+        <v>432</v>
+      </c>
+      <c r="C146" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="147" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A147" t="s">
+        <v>434</v>
+      </c>
+      <c r="B147" t="s">
+        <v>435</v>
+      </c>
+      <c r="C147" t="s">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="148" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A148" t="s">
+        <v>437</v>
+      </c>
+      <c r="B148" t="s">
+        <v>438</v>
+      </c>
+      <c r="C148" t="s">
+        <v>439</v>
+      </c>
+    </row>
+    <row r="149" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A149" t="s">
+        <v>440</v>
+      </c>
+      <c r="B149" t="s">
+        <v>441</v>
+      </c>
+      <c r="C149" t="s">
+        <v>442</v>
+      </c>
+    </row>
+    <row r="150" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A150" t="s">
+        <v>443</v>
+      </c>
+      <c r="B150" t="s">
+        <v>444</v>
+      </c>
+      <c r="C150" t="s">
+        <v>445</v>
+      </c>
+    </row>
+    <row r="151" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A151" t="s">
+        <v>446</v>
+      </c>
+      <c r="B151" t="s">
+        <v>447</v>
+      </c>
+      <c r="C151" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="152" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A152" t="s">
+        <v>449</v>
+      </c>
+      <c r="B152" t="s">
+        <v>450</v>
+      </c>
+      <c r="C152" t="s">
+        <v>451</v>
+      </c>
+    </row>
+    <row r="153" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A153" t="s">
+        <v>452</v>
+      </c>
+      <c r="B153" t="s">
+        <v>453</v>
+      </c>
+      <c r="C153" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="154" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A154" t="s">
+        <v>455</v>
+      </c>
+      <c r="B154" t="s">
+        <v>456</v>
+      </c>
+      <c r="C154" t="s">
+        <v>457</v>
+      </c>
+    </row>
+    <row r="155" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A155" t="s">
+        <v>458</v>
+      </c>
+      <c r="B155" t="s">
+        <v>459</v>
+      </c>
+      <c r="C155" t="s">
+        <v>460</v>
+      </c>
+    </row>
+    <row r="156" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A156" t="s">
+        <v>461</v>
+      </c>
+      <c r="B156" t="s">
+        <v>462</v>
+      </c>
+      <c r="C156" t="s">
+        <v>463</v>
+      </c>
+    </row>
+    <row r="157" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A157" t="s">
+        <v>464</v>
+      </c>
+      <c r="B157" t="s">
+        <v>465</v>
+      </c>
+      <c r="C157" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="158" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A158" t="s">
+        <v>467</v>
+      </c>
+      <c r="B158" t="s">
+        <v>468</v>
+      </c>
+      <c r="C158" t="s">
+        <v>469</v>
+      </c>
+    </row>
+    <row r="159" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A159" t="s">
+        <v>470</v>
+      </c>
+      <c r="B159" t="s">
+        <v>471</v>
+      </c>
+      <c r="C159" t="s">
+        <v>472</v>
+      </c>
+    </row>
+    <row r="160" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A160" t="s">
+        <v>473</v>
+      </c>
+      <c r="B160" t="s">
+        <v>474</v>
+      </c>
+      <c r="C160" t="s">
+        <v>475</v>
+      </c>
+    </row>
+    <row r="161" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A161" t="s">
+        <v>476</v>
+      </c>
+      <c r="B161" t="s">
+        <v>477</v>
+      </c>
+      <c r="C161" t="s">
+        <v>478</v>
+      </c>
+    </row>
+    <row r="162" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A162" t="s">
+        <v>479</v>
+      </c>
+      <c r="B162" t="s">
+        <v>480</v>
+      </c>
+      <c r="C162" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="163" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A163" t="s">
+        <v>482</v>
+      </c>
+      <c r="B163" t="s">
+        <v>483</v>
+      </c>
+      <c r="C163" t="s">
+        <v>484</v>
+      </c>
+    </row>
+    <row r="164" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A164" t="s">
+        <v>485</v>
+      </c>
+      <c r="B164" t="s">
+        <v>486</v>
+      </c>
+      <c r="C164" t="s">
+        <v>487</v>
+      </c>
+    </row>
+    <row r="165" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A165" t="s">
+        <v>488</v>
+      </c>
+      <c r="B165" t="s">
+        <v>489</v>
+      </c>
+      <c r="C165" t="s">
+        <v>490</v>
+      </c>
+    </row>
+    <row r="166" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A166" t="s">
+        <v>491</v>
+      </c>
+      <c r="B166" t="s">
+        <v>492</v>
+      </c>
+      <c r="C166" t="s">
+        <v>493</v>
+      </c>
+    </row>
+    <row r="167" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A167" t="s">
+        <v>494</v>
+      </c>
+      <c r="B167" t="s">
+        <v>495</v>
+      </c>
+      <c r="C167" t="s">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="168" spans="1:3" x14ac:dyDescent="0.55000000000000004">
+      <c r="A168" t="s">
+        <v>497</v>
+      </c>
+      <c r="B168" t="s">
+        <v>498</v>
+      </c>
+      <c r="C168" t="s">
+        <v>499</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
